--- a/_000_Global_Enum.xlsx
+++ b/_000_Global_Enum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7165975-CBCC-401A-AC4E-6BE9D9163C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6336C0-FC04-49F9-B0D6-B0AAF4FFFEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="90">
   <si>
     <t>Gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -367,6 +367,34 @@
   </si>
   <si>
     <t>Normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Storage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TimeOver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WorkCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetIt_ExpCard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Settings</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -797,15 +825,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
-  <dimension ref="A2:M24"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001"/>
+  <dimension ref="A2:N24"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.899999999999999"/>
   <cols>
-    <col min="1" max="19" width="15.640625" style="4" customWidth="1"/>
-    <col min="20" max="37" width="12.5703125" style="4" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="19" width="15.625" style="4" customWidth="1"/>
+    <col min="20" max="37" width="12.5625" style="4" customWidth="1"/>
+    <col min="38" max="16384" width="9.125" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" s="3" customFormat="1">
+    <row r="2" spans="1:14" s="3" customFormat="1">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -845,8 +873,11 @@
       <c r="M2" s="3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
         <v>37</v>
       </c>
@@ -886,8 +917,11 @@
       <c r="M3" s="4" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
@@ -927,8 +961,11 @@
       <c r="M4" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
         <v>39</v>
       </c>
@@ -961,8 +998,11 @@
       <c r="M5" s="4" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -991,8 +1031,11 @@
       <c r="M6" s="4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1017,13 +1060,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
@@ -1039,13 +1082,13 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:14">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
@@ -1058,13 +1101,13 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:14">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -1073,13 +1116,13 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:14">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -1088,13 +1131,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:14">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -1103,13 +1146,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:14">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -1118,13 +1161,13 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:14">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1133,13 +1176,13 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:14">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -1148,13 +1191,13 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:14">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -1169,7 +1212,7 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -1184,7 +1227,7 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -1199,7 +1242,7 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -1214,7 +1257,7 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1228,7 +1271,9 @@
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
+      <c r="E21" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -1241,7 +1286,9 @@
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
+      <c r="E22" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>

--- a/_000_Global_Enum.xlsx
+++ b/_000_Global_Enum.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6336C0-FC04-49F9-B0D6-B0AAF4FFFEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3CFF0D-7B5C-405B-8142-C43C4DB6E8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
@@ -370,10 +370,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Storage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MissionType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -395,6 +391,10 @@
   </si>
   <si>
     <t>Settings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inventory</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -874,7 +874,7 @@
         <v>77</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -918,7 +918,7 @@
         <v>82</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -962,7 +962,7 @@
         <v>81</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -999,7 +999,7 @@
         <v>80</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1032,7 +1032,7 @@
         <v>79</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1066,7 +1066,7 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
@@ -1227,7 +1227,7 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>

--- a/_000_Global_Enum.xlsx
+++ b/_000_Global_Enum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3CFF0D-7B5C-405B-8142-C43C4DB6E8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE5A980-B2E8-4D73-B929-C621F45FDE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="94">
   <si>
     <t>Gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -395,6 +395,22 @@
   </si>
   <si>
     <t>Inventory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemValueType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quantity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -825,7 +841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
-  <dimension ref="A2:N24"/>
+  <dimension ref="A2:O24"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="19" width="15.625" style="4" customWidth="1"/>
@@ -833,7 +849,7 @@
     <col min="38" max="16384" width="9.125" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" s="3" customFormat="1">
+    <row r="2" spans="1:15" s="3" customFormat="1">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -876,8 +892,11 @@
       <c r="N2" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
         <v>37</v>
       </c>
@@ -920,8 +939,11 @@
       <c r="N3" s="4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
@@ -964,8 +986,11 @@
       <c r="N4" s="4" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
         <v>39</v>
       </c>
@@ -1001,8 +1026,11 @@
       <c r="N5" s="4" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1034,8 +1062,11 @@
       <c r="N6" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1060,7 +1091,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1082,7 +1113,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1101,7 +1132,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1116,7 +1147,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1131,7 +1162,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1146,7 +1177,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1161,7 +1192,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:15">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1176,7 +1207,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:15">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1191,7 +1222,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:15">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>

--- a/_000_Global_Enum.xlsx
+++ b/_000_Global_Enum.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE5A980-B2E8-4D73-B929-C621F45FDE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE95BDC0-91DA-4984-9FD5-45891A76BECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="93">
   <si>
     <t>Gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -402,15 +402,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Level</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Quantity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Level</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -987,7 +983,7 @@
         <v>87</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -1027,7 +1023,7 @@
         <v>85</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1061,9 +1057,6 @@
       </c>
       <c r="N6" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:15">

--- a/_000_Global_Enum.xlsx
+++ b/_000_Global_Enum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE95BDC0-91DA-4984-9FD5-45891A76BECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1186AD10-187F-4F9E-B036-9AA02FD3B982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="97">
   <si>
     <t>Gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -407,6 +407,22 @@
   </si>
   <si>
     <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissionCycleType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Daily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weekly</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -837,7 +853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
-  <dimension ref="A2:O24"/>
+  <dimension ref="A2:P24"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="19" width="15.625" style="4" customWidth="1"/>
@@ -845,7 +861,7 @@
     <col min="38" max="16384" width="9.125" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" s="3" customFormat="1">
+    <row r="2" spans="1:16" s="3" customFormat="1">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -889,10 +905,13 @@
         <v>83</v>
       </c>
       <c r="O2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P2" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
         <v>37</v>
       </c>
@@ -933,13 +952,16 @@
         <v>82</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="O3" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="P3" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
@@ -980,13 +1002,16 @@
         <v>81</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O4" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="P4" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
         <v>39</v>
       </c>
@@ -1020,13 +1045,13 @@
         <v>80</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="O5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="P5" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:16">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1056,10 +1081,10 @@
         <v>79</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1083,8 +1108,11 @@
       <c r="M7" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1106,7 +1134,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:16">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1125,7 +1153,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:16">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1140,7 +1168,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:16">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1155,7 +1183,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:16">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1170,7 +1198,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:16">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1185,7 +1213,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:16">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1200,7 +1228,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:16">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1215,7 +1243,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:16">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1281,7 +1309,7 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1296,7 +1324,7 @@
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -1311,7 +1339,7 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -1322,7 +1350,9 @@
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
+      <c r="E23" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>

--- a/_000_Global_Enum.xlsx
+++ b/_000_Global_Enum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1186AD10-187F-4F9E-B036-9AA02FD3B982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2C43C1-8B67-4762-9AF5-B6FD27C42AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="99">
   <si>
     <t>Gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -423,6 +423,14 @@
   </si>
   <si>
     <t>Weekly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterSelect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TouchLock</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -430,7 +438,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -853,15 +861,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
-  <dimension ref="A2:P24"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.899999999999999"/>
+  <dimension ref="A2:P25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="19" width="15.625" style="4" customWidth="1"/>
     <col min="20" max="37" width="12.5625" style="4" customWidth="1"/>
     <col min="38" max="16384" width="9.125" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" s="3" customFormat="1">
+    <row r="2" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -911,7 +919,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>37</v>
       </c>
@@ -961,7 +969,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
@@ -1011,7 +1019,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A5" s="1" t="s">
         <v>39</v>
       </c>
@@ -1051,7 +1059,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1084,7 +1092,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1112,7 +1120,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1134,7 +1142,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1153,7 +1161,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1168,7 +1176,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1183,7 +1191,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1198,7 +1206,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1213,7 +1221,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1228,7 +1236,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1243,7 +1251,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1258,7 +1266,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1273,13 +1281,13 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -1288,13 +1296,13 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -1303,13 +1311,13 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1318,13 +1326,13 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -1333,39 +1341,46 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+      <c r="E24" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="E25" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/_000_Global_Enum.xlsx
+++ b/_000_Global_Enum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2C43C1-8B67-4762-9AF5-B6FD27C42AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640DDF3E-4B15-408E-9444-E26B4C1422F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="100">
   <si>
     <t>Gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -431,6 +431,10 @@
   </si>
   <si>
     <t>TouchLock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardBox</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -861,7 +865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
-  <dimension ref="A2:P25"/>
+  <dimension ref="A2:P26"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="19" width="15.625" style="4" customWidth="1"/>
@@ -1317,7 +1321,7 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1332,7 +1336,7 @@
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -1347,7 +1351,7 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -1359,7 +1363,7 @@
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="1" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -1371,7 +1375,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -1379,6 +1383,11 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.6">
       <c r="E25" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="E26" s="1" t="s">
         <v>28</v>
       </c>
     </row>

--- a/_000_Global_Enum.xlsx
+++ b/_000_Global_Enum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640DDF3E-4B15-408E-9444-E26B4C1422F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49734456-A48D-4317-BEB7-BFE9ABB5291C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="4050" yWindow="3308" windowWidth="21600" windowHeight="11332" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -142,18 +142,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Group_0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Group_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Group_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Crystal</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -435,6 +423,18 @@
   </si>
   <si>
     <t>RewardBox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Board_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Board_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Board_2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -442,7 +442,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -865,15 +865,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
-  <dimension ref="A2:P26"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <dimension ref="A2:P28"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="19" width="15.625" style="4" customWidth="1"/>
     <col min="20" max="37" width="12.5625" style="4" customWidth="1"/>
     <col min="38" max="16384" width="9.125" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:16" s="3" customFormat="1">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -899,48 +899,48 @@
         <v>8</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.6">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>9</v>
@@ -949,45 +949,45 @@
         <v>9</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.6">
-      <c r="A4" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>0</v>
@@ -999,44 +999,44 @@
         <v>10</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="N4" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="O4" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.6">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>11</v>
@@ -1045,34 +1045,34 @@
         <v>11</v>
       </c>
       <c r="I5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="K5" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.6">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>12</v>
@@ -1081,315 +1081,321 @@
         <v>12</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.6">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.6">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.6">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.6">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="K10" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.6">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="K11" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.6">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="K12" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.6">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="K13" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.6">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="K14" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="K15" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.6">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="K16" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="K17" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="K18" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="K19" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="K20" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.6">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="K21" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.6">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:11">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="1" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:11">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="1" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:11">
       <c r="E25" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.6">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="E26" s="1" t="s">
-        <v>28</v>
-      </c>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="E28" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/_000_Global_Enum.xlsx
+++ b/_000_Global_Enum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49734456-A48D-4317-BEB7-BFE9ABB5291C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BA6239-631C-4453-B4A4-4E762374E871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4050" yWindow="3308" windowWidth="21600" windowHeight="11332" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="104">
   <si>
     <t>Gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -126,10 +126,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Works</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Notice</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -436,13 +432,31 @@
   <si>
     <t>Board_2</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageSelect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_2</t>
+  </si>
+  <si>
+    <t>_3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -865,15 +879,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
-  <dimension ref="A2:P28"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.899999999999999"/>
+  <dimension ref="A2:Q28"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="19" width="15.625" style="4" customWidth="1"/>
     <col min="20" max="37" width="12.5625" style="4" customWidth="1"/>
     <col min="38" max="16384" width="9.125" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" s="3" customFormat="1">
+    <row r="2" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -899,48 +913,51 @@
         <v>8</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+        <v>86</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>9</v>
@@ -949,42 +966,45 @@
         <v>9</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>13</v>
@@ -999,44 +1019,47 @@
         <v>10</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>73</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>11</v>
@@ -1045,25 +1068,28 @@
         <v>11</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>87</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1072,7 +1098,7 @@
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>12</v>
@@ -1081,22 +1107,22 @@
         <v>12</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1106,25 +1132,25 @@
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1134,38 +1160,38 @@
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1177,10 +1203,10 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="K10" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1192,10 +1218,10 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="K11" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1207,10 +1233,10 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="K12" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1222,179 +1248,179 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="K13" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="K14" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="K15" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="K16" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="K17" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="K18" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="K19" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="K20" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="K21" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.6">
       <c r="E25" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.6">
       <c r="E26" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.6">
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.6">
       <c r="E28" s="1"/>
     </row>
   </sheetData>
